--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -461,10 +461,10 @@
         <v>2026-05-15</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="str">
-        <v>Completado</v>
+        <v>En progreso</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -496,10 +496,10 @@
         <v>2026-05-15</v>
       </c>
       <c r="I3">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="J3" t="str">
-        <v>En progreso</v>
+        <v>Completado</v>
       </c>
       <c r="K3" t="str">
         <v/>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -461,10 +461,10 @@
         <v>2026-05-15</v>
       </c>
       <c r="I2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J2" t="str">
-        <v>En progreso</v>
+        <v>Completado</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -881,7 +881,7 @@
         <v>2026-09-25</v>
       </c>
       <c r="I14">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="str">
         <v>En progreso</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -461,10 +461,10 @@
         <v>2026-05-15</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J2" t="str">
-        <v>Completado</v>
+        <v>En progreso</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -881,7 +881,7 @@
         <v>2026-09-25</v>
       </c>
       <c r="I14">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J14" t="str">
         <v>En progreso</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -461,10 +461,10 @@
         <v>2026-05-15</v>
       </c>
       <c r="I2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J2" t="str">
-        <v>En progreso</v>
+        <v>Completado</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -881,7 +881,7 @@
         <v>2026-09-25</v>
       </c>
       <c r="I14">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="str">
         <v>En progreso</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -449,22 +449,22 @@
         <v>Expansión</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-31</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-19</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-31</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-14</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="J2" t="str">
-        <v>Completado</v>
+        <v>En progreso</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -484,16 +484,16 @@
         <v>Expansión</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-31</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-21</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-31</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-14</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -519,16 +519,16 @@
         <v>Expansión</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-23</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-05</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-07-06</v>
+        <v>2026-07-05</v>
       </c>
       <c r="I4">
         <v>0.5</v>
@@ -554,16 +554,16 @@
         <v>Expansión</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-26</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-05</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-26</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -589,16 +589,16 @@
         <v>Expansión</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-12</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-12</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-09</v>
       </c>
       <c r="I6">
         <v>0.5</v>
@@ -624,16 +624,16 @@
         <v>Expansión</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-12</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-05-01</v>
+        <v>2026-04-30</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-12</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-13</v>
       </c>
       <c r="I7">
         <v>0.5</v>
@@ -659,16 +659,16 @@
         <v>Expansión</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-19</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-03</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-19</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-07-17</v>
+        <v>2026-07-16</v>
       </c>
       <c r="I8">
         <v>0.5</v>
@@ -694,16 +694,16 @@
         <v>Expansión</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-19</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-05</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-19</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-07-22</v>
+        <v>2026-07-21</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -729,16 +729,16 @@
         <v>Expansión</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-26</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-07</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-26</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-26</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -764,16 +764,16 @@
         <v>Expansión</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-26</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-10</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-26</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-07-31</v>
+        <v>2026-07-30</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -799,16 +799,16 @@
         <v>Expansión</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-12</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-01</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-06-13</v>
+        <v>2026-06-12</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-02</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -834,16 +834,16 @@
         <v>Expansión</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-07</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-26</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-07</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-28</v>
+        <v>2026-08-27</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -869,16 +869,16 @@
         <v>Expansión</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-07-06</v>
+        <v>2026-07-05</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-07-25</v>
+        <v>2026-07-24</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-09-06</v>
+        <v>2026-09-05</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-09-25</v>
+        <v>2026-09-24</v>
       </c>
       <c r="I14">
         <v>0.6</v>
@@ -904,16 +904,16 @@
         <v>Expansión</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-03</v>
+        <v>2026-08-02</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-08-29</v>
+        <v>2026-08-28</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-02</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-29</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -939,16 +939,16 @@
         <v>Expansión</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-09-07</v>
+        <v>2026-09-06</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-25</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-11-07</v>
+        <v>2026-11-06</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-11-27</v>
+        <v>2026-11-26</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -974,16 +974,16 @@
         <v>Expansión</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-04</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-23</v>
       </c>
       <c r="G17" t="str">
-        <v>2026-12-05</v>
+        <v>2026-12-04</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-12-25</v>
+        <v>2026-12-24</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1009,16 +1009,16 @@
         <v>Expansión</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-11-02</v>
+        <v>2026-11-01</v>
       </c>
       <c r="F18" t="str">
-        <v>2026-11-21</v>
+        <v>2026-11-20</v>
       </c>
       <c r="G18" t="str">
-        <v>2027-01-02</v>
+        <v>2027-01-01</v>
       </c>
       <c r="H18" t="str">
-        <v>2027-01-22</v>
+        <v>2027-01-21</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1044,16 +1044,16 @@
         <v>Expansión</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-11-30</v>
+        <v>2026-11-29</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-12-19</v>
+        <v>2026-12-18</v>
       </c>
       <c r="G19" t="str">
-        <v>2027-01-30</v>
+        <v>2027-01-29</v>
       </c>
       <c r="H19" t="str">
-        <v>2027-02-19</v>
+        <v>2027-02-18</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1079,16 +1079,16 @@
         <v>Expansión</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-12-28</v>
+        <v>2026-12-27</v>
       </c>
       <c r="F20" t="str">
-        <v>2027-01-23</v>
+        <v>2027-01-22</v>
       </c>
       <c r="G20" t="str">
-        <v>2027-02-28</v>
+        <v>2027-02-27</v>
       </c>
       <c r="H20" t="str">
-        <v>2027-03-26</v>
+        <v>2027-03-25</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1114,16 +1114,16 @@
         <v>Expansión</v>
       </c>
       <c r="E21" t="str">
-        <v>2027-02-01</v>
+        <v>2027-01-31</v>
       </c>
       <c r="F21" t="str">
-        <v>2027-02-20</v>
+        <v>2027-02-19</v>
       </c>
       <c r="G21" t="str">
-        <v>2027-04-01</v>
+        <v>2027-03-31</v>
       </c>
       <c r="H21" t="str">
-        <v>2027-04-22</v>
+        <v>2027-04-21</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1149,16 +1149,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-03</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-29</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-03</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-29</v>
       </c>
       <c r="I22">
         <v>0.5</v>
@@ -1184,16 +1184,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-07-06</v>
+        <v>2026-07-05</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-31</v>
       </c>
       <c r="G23" t="str">
-        <v>2026-07-06</v>
+        <v>2026-07-05</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-30</v>
       </c>
       <c r="I23">
         <v>0.4</v>
@@ -1219,16 +1219,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-09</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-09-12</v>
+        <v>2026-09-11</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-09</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-11-12</v>
+        <v>2026-11-11</v>
       </c>
       <c r="I24">
         <v>0.1</v>
@@ -1254,16 +1254,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-20</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-10-17</v>
+        <v>2026-10-16</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-20</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-12-17</v>
+        <v>2026-12-16</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1289,16 +1289,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-11-21</v>
+        <v>2026-11-20</v>
       </c>
       <c r="G26" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="H26" t="str">
-        <v>2027-01-21</v>
+        <v>2027-01-20</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1324,16 +1324,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-11-30</v>
+        <v>2026-11-29</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-12-26</v>
+        <v>2026-12-25</v>
       </c>
       <c r="G27" t="str">
-        <v>2026-11-30</v>
+        <v>2026-11-29</v>
       </c>
       <c r="H27" t="str">
-        <v>2027-02-26</v>
+        <v>2027-02-25</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1359,16 +1359,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E28" t="str">
-        <v>2027-01-04</v>
+        <v>2027-01-03</v>
       </c>
       <c r="F28" t="str">
-        <v>2027-01-30</v>
+        <v>2027-01-29</v>
       </c>
       <c r="G28" t="str">
-        <v>2027-01-04</v>
+        <v>2027-01-03</v>
       </c>
       <c r="H28" t="str">
-        <v>2027-03-30</v>
+        <v>2027-03-29</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1394,16 +1394,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E29" t="str">
-        <v>2027-02-08</v>
+        <v>2027-02-07</v>
       </c>
       <c r="F29" t="str">
-        <v>2027-03-06</v>
+        <v>2027-03-05</v>
       </c>
       <c r="G29" t="str">
-        <v>2027-02-08</v>
+        <v>2027-02-07</v>
       </c>
       <c r="H29" t="str">
-        <v>2027-05-06</v>
+        <v>2027-05-05</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1429,16 +1429,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E30" t="str">
-        <v>2027-03-15</v>
+        <v>2027-03-14</v>
       </c>
       <c r="F30" t="str">
-        <v>2027-04-10</v>
+        <v>2027-04-09</v>
       </c>
       <c r="G30" t="str">
-        <v>2027-03-15</v>
+        <v>2027-03-14</v>
       </c>
       <c r="H30" t="str">
-        <v>2027-06-10</v>
+        <v>2027-06-09</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1464,16 +1464,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E31" t="str">
-        <v>2027-04-19</v>
+        <v>2027-04-18</v>
       </c>
       <c r="F31" t="str">
-        <v>2027-05-15</v>
+        <v>2027-05-14</v>
       </c>
       <c r="G31" t="str">
-        <v>2027-04-19</v>
+        <v>2027-04-18</v>
       </c>
       <c r="H31" t="str">
-        <v>2027-07-02</v>
+        <v>2027-07-01</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1499,16 +1499,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-31</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-21</v>
       </c>
       <c r="G32" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-31</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-22</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-03</v>
+        <v>2026-08-02</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-23</v>
       </c>
       <c r="G33" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-02</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-12-25</v>
+        <v>2026-12-24</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1569,16 +1569,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-13</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-12-05</v>
+        <v>2026-12-04</v>
       </c>
       <c r="G34" t="str">
-        <v>2026-11-14</v>
+        <v>2026-11-13</v>
       </c>
       <c r="H34" t="str">
-        <v>2027-02-05</v>
+        <v>2027-02-04</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1604,16 +1604,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-18</v>
       </c>
       <c r="F35" t="str">
-        <v>2027-01-09</v>
+        <v>2027-01-08</v>
       </c>
       <c r="G35" t="str">
-        <v>2026-12-19</v>
+        <v>2026-12-18</v>
       </c>
       <c r="H35" t="str">
-        <v>2027-03-12</v>
+        <v>2027-03-11</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1639,16 +1639,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-11-23</v>
+        <v>2026-11-22</v>
       </c>
       <c r="F36" t="str">
-        <v>2027-02-13</v>
+        <v>2027-02-12</v>
       </c>
       <c r="G36" t="str">
-        <v>2027-01-23</v>
+        <v>2027-01-22</v>
       </c>
       <c r="H36" t="str">
-        <v>2027-04-16</v>
+        <v>2027-04-15</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1674,16 +1674,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-12-28</v>
+        <v>2026-12-27</v>
       </c>
       <c r="F37" t="str">
-        <v>2027-03-20</v>
+        <v>2027-03-19</v>
       </c>
       <c r="G37" t="str">
-        <v>2027-02-28</v>
+        <v>2027-02-27</v>
       </c>
       <c r="H37" t="str">
-        <v>2027-05-21</v>
+        <v>2027-05-20</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1709,16 +1709,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E38" t="str">
-        <v>2027-02-01</v>
+        <v>2027-01-31</v>
       </c>
       <c r="F38" t="str">
-        <v>2027-04-24</v>
+        <v>2027-04-23</v>
       </c>
       <c r="G38" t="str">
-        <v>2027-04-01</v>
+        <v>2027-03-31</v>
       </c>
       <c r="H38" t="str">
-        <v>2027-06-24</v>
+        <v>2027-06-23</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -1744,16 +1744,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E39" t="str">
-        <v>2027-03-08</v>
+        <v>2027-03-07</v>
       </c>
       <c r="F39" t="str">
-        <v>2027-05-29</v>
+        <v>2027-05-28</v>
       </c>
       <c r="G39" t="str">
-        <v>2027-05-08</v>
+        <v>2027-05-07</v>
       </c>
       <c r="H39" t="str">
-        <v>2027-07-30</v>
+        <v>2027-07-29</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -1779,16 +1779,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E40" t="str">
-        <v>2027-04-12</v>
+        <v>2027-04-11</v>
       </c>
       <c r="F40" t="str">
-        <v>2027-07-03</v>
+        <v>2027-07-02</v>
       </c>
       <c r="G40" t="str">
-        <v>2027-06-12</v>
+        <v>2027-06-11</v>
       </c>
       <c r="H40" t="str">
-        <v>2027-09-03</v>
+        <v>2027-09-02</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -1814,16 +1814,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E41" t="str">
-        <v>2027-05-17</v>
+        <v>2027-05-16</v>
       </c>
       <c r="F41" t="str">
-        <v>2027-08-07</v>
+        <v>2027-08-06</v>
       </c>
       <c r="G41" t="str">
-        <v>2027-07-17</v>
+        <v>2027-07-16</v>
       </c>
       <c r="H41" t="str">
-        <v>2027-10-08</v>
+        <v>2027-10-07</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>Obras</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-26</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-11-14</v>
+        <v>2026-11-13</v>
       </c>
       <c r="G42" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-26</v>
       </c>
       <c r="H42" t="str">
-        <v>2027-01-15</v>
+        <v>2027-01-14</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -1884,16 +1884,16 @@
         <v>Obras</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-27</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-12-19</v>
+        <v>2026-12-18</v>
       </c>
       <c r="G43" t="str">
-        <v>2026-11-28</v>
+        <v>2026-11-27</v>
       </c>
       <c r="H43" t="str">
-        <v>2027-02-19</v>
+        <v>2027-02-18</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -1919,16 +1919,16 @@
         <v>Obras</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-11-09</v>
+        <v>2026-11-08</v>
       </c>
       <c r="F44" t="str">
-        <v>2027-02-27</v>
+        <v>2027-02-26</v>
       </c>
       <c r="G44" t="str">
-        <v>2027-01-09</v>
+        <v>2027-01-08</v>
       </c>
       <c r="H44" t="str">
-        <v>2027-04-30</v>
+        <v>2027-04-29</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -1954,16 +1954,16 @@
         <v>Obras</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-12-14</v>
+        <v>2026-12-13</v>
       </c>
       <c r="F45" t="str">
-        <v>2027-04-03</v>
+        <v>2027-04-02</v>
       </c>
       <c r="G45" t="str">
-        <v>2027-02-14</v>
+        <v>2027-02-13</v>
       </c>
       <c r="H45" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-03</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -1989,16 +1989,16 @@
         <v>Obras</v>
       </c>
       <c r="E46" t="str">
-        <v>2027-01-18</v>
+        <v>2027-01-17</v>
       </c>
       <c r="F46" t="str">
-        <v>2027-05-08</v>
+        <v>2027-05-07</v>
       </c>
       <c r="G46" t="str">
-        <v>2027-03-18</v>
+        <v>2027-03-17</v>
       </c>
       <c r="H46" t="str">
-        <v>2027-07-08</v>
+        <v>2027-07-07</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2024,16 +2024,16 @@
         <v>Obras</v>
       </c>
       <c r="E47" t="str">
-        <v>2027-02-22</v>
+        <v>2027-02-21</v>
       </c>
       <c r="F47" t="str">
-        <v>2027-06-12</v>
+        <v>2027-06-11</v>
       </c>
       <c r="G47" t="str">
-        <v>2027-04-22</v>
+        <v>2027-04-21</v>
       </c>
       <c r="H47" t="str">
-        <v>2027-08-12</v>
+        <v>2027-08-11</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2059,16 +2059,16 @@
         <v>Obras</v>
       </c>
       <c r="E48" t="str">
-        <v>2027-03-29</v>
+        <v>2027-03-28</v>
       </c>
       <c r="F48" t="str">
-        <v>2027-07-17</v>
+        <v>2027-07-16</v>
       </c>
       <c r="G48" t="str">
-        <v>2027-05-29</v>
+        <v>2027-05-28</v>
       </c>
       <c r="H48" t="str">
-        <v>2027-09-17</v>
+        <v>2027-09-16</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2094,16 +2094,16 @@
         <v>Obras</v>
       </c>
       <c r="E49" t="str">
-        <v>2027-05-03</v>
+        <v>2027-05-02</v>
       </c>
       <c r="F49" t="str">
-        <v>2027-08-21</v>
+        <v>2027-08-20</v>
       </c>
       <c r="G49" t="str">
-        <v>2027-07-03</v>
+        <v>2027-07-02</v>
       </c>
       <c r="H49" t="str">
-        <v>2027-10-22</v>
+        <v>2027-10-21</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2129,16 +2129,16 @@
         <v>Obras</v>
       </c>
       <c r="E50" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-06</v>
       </c>
       <c r="F50" t="str">
-        <v>2027-09-25</v>
+        <v>2027-09-24</v>
       </c>
       <c r="G50" t="str">
-        <v>2027-08-07</v>
+        <v>2027-08-06</v>
       </c>
       <c r="H50" t="str">
-        <v>2027-11-26</v>
+        <v>2027-11-25</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2164,16 +2164,16 @@
         <v>Obras</v>
       </c>
       <c r="E51" t="str">
-        <v>2027-07-12</v>
+        <v>2027-07-11</v>
       </c>
       <c r="F51" t="str">
-        <v>2027-10-30</v>
+        <v>2027-10-29</v>
       </c>
       <c r="G51" t="str">
-        <v>2027-09-12</v>
+        <v>2027-09-11</v>
       </c>
       <c r="H51" t="str">
-        <v>2027-12-31</v>
+        <v>2027-12-30</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2199,16 +2199,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-26</v>
       </c>
       <c r="F52" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-18</v>
       </c>
       <c r="G52" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-26</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-11-20</v>
+        <v>2026-11-19</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2234,16 +2234,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-11</v>
       </c>
       <c r="F53" t="str">
-        <v>2026-12-05</v>
+        <v>2026-12-04</v>
       </c>
       <c r="G53" t="str">
-        <v>2026-12-12</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H53" t="str">
-        <v>2027-02-05</v>
+        <v>2027-02-04</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2269,16 +2269,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-11-09</v>
+        <v>2026-11-08</v>
       </c>
       <c r="F54" t="str">
-        <v>2027-01-02</v>
+        <v>2027-01-01</v>
       </c>
       <c r="G54" t="str">
-        <v>2027-01-09</v>
+        <v>2027-01-08</v>
       </c>
       <c r="H54" t="str">
-        <v>2027-03-05</v>
+        <v>2027-03-04</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2304,16 +2304,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-12-14</v>
+        <v>2026-12-13</v>
       </c>
       <c r="F55" t="str">
-        <v>2027-02-06</v>
+        <v>2027-02-05</v>
       </c>
       <c r="G55" t="str">
-        <v>2027-02-14</v>
+        <v>2027-02-13</v>
       </c>
       <c r="H55" t="str">
-        <v>2027-04-09</v>
+        <v>2027-04-08</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2339,16 +2339,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E56" t="str">
-        <v>2027-01-18</v>
+        <v>2027-01-17</v>
       </c>
       <c r="F56" t="str">
-        <v>2027-03-13</v>
+        <v>2027-03-12</v>
       </c>
       <c r="G56" t="str">
-        <v>2027-03-18</v>
+        <v>2027-03-17</v>
       </c>
       <c r="H56" t="str">
-        <v>2027-05-13</v>
+        <v>2027-05-12</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2374,16 +2374,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E57" t="str">
-        <v>2027-02-22</v>
+        <v>2027-02-21</v>
       </c>
       <c r="F57" t="str">
-        <v>2027-04-17</v>
+        <v>2027-04-16</v>
       </c>
       <c r="G57" t="str">
-        <v>2027-04-22</v>
+        <v>2027-04-21</v>
       </c>
       <c r="H57" t="str">
-        <v>2027-06-17</v>
+        <v>2027-06-16</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2409,16 +2409,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E58" t="str">
-        <v>2027-03-29</v>
+        <v>2027-03-28</v>
       </c>
       <c r="F58" t="str">
-        <v>2027-05-22</v>
+        <v>2027-05-21</v>
       </c>
       <c r="G58" t="str">
-        <v>2027-05-29</v>
+        <v>2027-05-28</v>
       </c>
       <c r="H58" t="str">
-        <v>2027-07-23</v>
+        <v>2027-07-22</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2444,16 +2444,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E59" t="str">
-        <v>2027-05-03</v>
+        <v>2027-05-02</v>
       </c>
       <c r="F59" t="str">
-        <v>2027-06-26</v>
+        <v>2027-06-25</v>
       </c>
       <c r="G59" t="str">
-        <v>2027-07-03</v>
+        <v>2027-07-02</v>
       </c>
       <c r="H59" t="str">
-        <v>2027-08-27</v>
+        <v>2027-08-26</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2479,16 +2479,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E60" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-06</v>
       </c>
       <c r="F60" t="str">
-        <v>2027-07-31</v>
+        <v>2027-07-30</v>
       </c>
       <c r="G60" t="str">
-        <v>2027-08-07</v>
+        <v>2027-08-06</v>
       </c>
       <c r="H60" t="str">
-        <v>2027-10-01</v>
+        <v>2027-09-30</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2514,16 +2514,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E61" t="str">
-        <v>2027-07-12</v>
+        <v>2027-07-11</v>
       </c>
       <c r="F61" t="str">
-        <v>2027-09-04</v>
+        <v>2027-09-03</v>
       </c>
       <c r="G61" t="str">
-        <v>2027-09-12</v>
+        <v>2027-09-11</v>
       </c>
       <c r="H61" t="str">
-        <v>2027-11-05</v>
+        <v>2027-11-04</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2549,16 +2549,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-20</v>
       </c>
       <c r="F62" t="str">
-        <v>2026-11-14</v>
+        <v>2026-11-13</v>
       </c>
       <c r="G62" t="str">
-        <v>2026-11-21</v>
+        <v>2026-11-20</v>
       </c>
       <c r="H62" t="str">
-        <v>2027-01-15</v>
+        <v>2027-01-14</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2584,16 +2584,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-12-07</v>
+        <v>2026-12-06</v>
       </c>
       <c r="F63" t="str">
-        <v>2027-01-30</v>
+        <v>2027-01-29</v>
       </c>
       <c r="G63" t="str">
-        <v>2027-02-07</v>
+        <v>2027-02-06</v>
       </c>
       <c r="H63" t="str">
-        <v>2027-04-02</v>
+        <v>2027-04-01</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2619,16 +2619,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E64" t="str">
-        <v>2027-01-04</v>
+        <v>2027-01-03</v>
       </c>
       <c r="F64" t="str">
-        <v>2027-02-27</v>
+        <v>2027-02-26</v>
       </c>
       <c r="G64" t="str">
-        <v>2027-03-04</v>
+        <v>2027-03-03</v>
       </c>
       <c r="H64" t="str">
-        <v>2027-04-29</v>
+        <v>2027-04-28</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E65" t="str">
-        <v>2027-02-08</v>
+        <v>2027-02-07</v>
       </c>
       <c r="F65" t="str">
-        <v>2027-04-03</v>
+        <v>2027-04-02</v>
       </c>
       <c r="G65" t="str">
-        <v>2027-04-08</v>
+        <v>2027-04-07</v>
       </c>
       <c r="H65" t="str">
-        <v>2027-06-03</v>
+        <v>2027-06-02</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2689,16 +2689,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E66" t="str">
-        <v>2027-03-15</v>
+        <v>2027-03-14</v>
       </c>
       <c r="F66" t="str">
-        <v>2027-05-08</v>
+        <v>2027-05-07</v>
       </c>
       <c r="G66" t="str">
-        <v>2027-05-15</v>
+        <v>2027-05-14</v>
       </c>
       <c r="H66" t="str">
-        <v>2027-07-09</v>
+        <v>2027-07-08</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -2724,16 +2724,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E67" t="str">
-        <v>2027-04-19</v>
+        <v>2027-04-18</v>
       </c>
       <c r="F67" t="str">
-        <v>2027-06-12</v>
+        <v>2027-06-11</v>
       </c>
       <c r="G67" t="str">
-        <v>2027-06-19</v>
+        <v>2027-06-18</v>
       </c>
       <c r="H67" t="str">
-        <v>2027-08-13</v>
+        <v>2027-08-12</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2759,16 +2759,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E68" t="str">
-        <v>2027-05-24</v>
+        <v>2027-05-23</v>
       </c>
       <c r="F68" t="str">
-        <v>2027-07-17</v>
+        <v>2027-07-16</v>
       </c>
       <c r="G68" t="str">
-        <v>2027-07-24</v>
+        <v>2027-07-23</v>
       </c>
       <c r="H68" t="str">
-        <v>2027-09-17</v>
+        <v>2027-09-16</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -2794,16 +2794,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E69" t="str">
-        <v>2027-06-28</v>
+        <v>2027-06-27</v>
       </c>
       <c r="F69" t="str">
-        <v>2027-08-21</v>
+        <v>2027-08-20</v>
       </c>
       <c r="G69" t="str">
-        <v>2027-08-28</v>
+        <v>2027-08-27</v>
       </c>
       <c r="H69" t="str">
-        <v>2027-10-22</v>
+        <v>2027-10-21</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -2829,16 +2829,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E70" t="str">
-        <v>2027-08-02</v>
+        <v>2027-08-01</v>
       </c>
       <c r="F70" t="str">
-        <v>2027-09-25</v>
+        <v>2027-09-24</v>
       </c>
       <c r="G70" t="str">
-        <v>2027-10-02</v>
+        <v>2027-10-01</v>
       </c>
       <c r="H70" t="str">
-        <v>2027-11-26</v>
+        <v>2027-11-25</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -2864,16 +2864,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E71" t="str">
-        <v>2027-09-06</v>
+        <v>2027-09-05</v>
       </c>
       <c r="F71" t="str">
-        <v>2027-10-30</v>
+        <v>2027-10-29</v>
       </c>
       <c r="G71" t="str">
-        <v>2027-11-06</v>
+        <v>2027-11-05</v>
       </c>
       <c r="H71" t="str">
-        <v>2027-12-31</v>
+        <v>2027-12-30</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -2899,16 +2899,16 @@
         <v>Dirección</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-11-30</v>
+        <v>2026-11-29</v>
       </c>
       <c r="F72" t="str">
-        <v>2026-11-30</v>
+        <v>2026-11-29</v>
       </c>
       <c r="G72" t="str">
-        <v>2027-02-01</v>
+        <v>2027-01-31</v>
       </c>
       <c r="H72" t="str">
-        <v>2027-02-01</v>
+        <v>2027-01-31</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -2934,16 +2934,16 @@
         <v>Dirección</v>
       </c>
       <c r="E73" t="str">
-        <v>2027-02-15</v>
+        <v>2027-02-14</v>
       </c>
       <c r="F73" t="str">
-        <v>2027-02-15</v>
+        <v>2027-02-14</v>
       </c>
       <c r="G73" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-14</v>
       </c>
       <c r="H73" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-14</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -2969,16 +2969,16 @@
         <v>Dirección</v>
       </c>
       <c r="E74" t="str">
-        <v>2027-03-15</v>
+        <v>2027-03-14</v>
       </c>
       <c r="F74" t="str">
-        <v>2027-03-15</v>
+        <v>2027-03-14</v>
       </c>
       <c r="G74" t="str">
-        <v>2027-05-15</v>
+        <v>2027-05-14</v>
       </c>
       <c r="H74" t="str">
-        <v>2027-05-15</v>
+        <v>2027-05-14</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3004,16 +3004,16 @@
         <v>Dirección</v>
       </c>
       <c r="E75" t="str">
-        <v>2027-04-19</v>
+        <v>2027-04-18</v>
       </c>
       <c r="F75" t="str">
-        <v>2027-04-19</v>
+        <v>2027-04-18</v>
       </c>
       <c r="G75" t="str">
-        <v>2027-06-19</v>
+        <v>2027-06-18</v>
       </c>
       <c r="H75" t="str">
-        <v>2027-06-19</v>
+        <v>2027-06-18</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3039,16 +3039,16 @@
         <v>Dirección</v>
       </c>
       <c r="E76" t="str">
-        <v>2027-05-24</v>
+        <v>2027-05-23</v>
       </c>
       <c r="F76" t="str">
-        <v>2027-05-24</v>
+        <v>2027-05-23</v>
       </c>
       <c r="G76" t="str">
-        <v>2027-07-24</v>
+        <v>2027-07-23</v>
       </c>
       <c r="H76" t="str">
-        <v>2027-07-24</v>
+        <v>2027-07-23</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3074,16 +3074,16 @@
         <v>Dirección</v>
       </c>
       <c r="E77" t="str">
-        <v>2027-06-28</v>
+        <v>2027-06-27</v>
       </c>
       <c r="F77" t="str">
-        <v>2027-06-28</v>
+        <v>2027-06-27</v>
       </c>
       <c r="G77" t="str">
-        <v>2027-08-28</v>
+        <v>2027-08-27</v>
       </c>
       <c r="H77" t="str">
-        <v>2027-08-28</v>
+        <v>2027-08-27</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3109,16 +3109,16 @@
         <v>Dirección</v>
       </c>
       <c r="E78" t="str">
-        <v>2027-08-02</v>
+        <v>2027-08-01</v>
       </c>
       <c r="F78" t="str">
-        <v>2027-08-02</v>
+        <v>2027-08-01</v>
       </c>
       <c r="G78" t="str">
-        <v>2027-10-02</v>
+        <v>2027-10-01</v>
       </c>
       <c r="H78" t="str">
-        <v>2027-10-02</v>
+        <v>2027-10-01</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3144,16 +3144,16 @@
         <v>Dirección</v>
       </c>
       <c r="E79" t="str">
-        <v>2027-09-05</v>
+        <v>2027-09-04</v>
       </c>
       <c r="F79" t="str">
-        <v>2027-09-05</v>
+        <v>2027-09-04</v>
       </c>
       <c r="G79" t="str">
-        <v>2027-11-05</v>
+        <v>2027-11-04</v>
       </c>
       <c r="H79" t="str">
-        <v>2027-11-05</v>
+        <v>2027-11-04</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3179,16 +3179,16 @@
         <v>Dirección</v>
       </c>
       <c r="E80" t="str">
-        <v>2027-10-11</v>
+        <v>2027-10-10</v>
       </c>
       <c r="F80" t="str">
-        <v>2027-10-11</v>
+        <v>2027-10-10</v>
       </c>
       <c r="G80" t="str">
-        <v>2027-12-11</v>
+        <v>2027-12-10</v>
       </c>
       <c r="H80" t="str">
-        <v>2027-12-11</v>
+        <v>2027-12-10</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3214,16 +3214,16 @@
         <v>Dirección</v>
       </c>
       <c r="E81" t="str">
-        <v>2027-11-15</v>
+        <v>2027-11-14</v>
       </c>
       <c r="F81" t="str">
-        <v>2027-11-15</v>
+        <v>2027-11-14</v>
       </c>
       <c r="G81" t="str">
-        <v>2028-01-15</v>
+        <v>2028-01-14</v>
       </c>
       <c r="H81" t="str">
-        <v>2028-01-15</v>
+        <v>2028-01-14</v>
       </c>
       <c r="I81">
         <v>0</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -461,10 +461,10 @@
         <v>2026-05-14</v>
       </c>
       <c r="I2">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="J2" t="str">
-        <v>En progreso</v>
+        <v>Completado</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -916,10 +916,10 @@
         <v>2026-10-29</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J15" t="str">
-        <v>Pendiente</v>
+        <v>En progreso</v>
       </c>
       <c r="K15" t="str">
         <v/>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -449,22 +449,22 @@
         <v>Expansión</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-03-31</v>
+        <v>2026-03-30</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-18</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-03-31</v>
+        <v>2026-03-30</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-13</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="J2" t="str">
-        <v>Completado</v>
+        <v>En progreso</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -484,16 +484,16 @@
         <v>Expansión</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-03-31</v>
+        <v>2026-03-30</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-20</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-03-31</v>
+        <v>2026-03-30</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-13</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -519,16 +519,16 @@
         <v>Expansión</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-04</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-22</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-04</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-04</v>
       </c>
       <c r="I4">
         <v>0.5</v>
@@ -554,16 +554,16 @@
         <v>Expansión</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-04</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-25</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-04</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-25</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -589,16 +589,16 @@
         <v>Expansión</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-11</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-04-28</v>
+        <v>2026-04-27</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-11</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-07-09</v>
+        <v>2026-07-08</v>
       </c>
       <c r="I6">
         <v>0.5</v>
@@ -624,16 +624,16 @@
         <v>Expansión</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-11</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-04-30</v>
+        <v>2026-04-29</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-11</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-12</v>
       </c>
       <c r="I7">
         <v>0.5</v>
@@ -659,16 +659,16 @@
         <v>Expansión</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-18</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-02</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-18</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-07-16</v>
+        <v>2026-07-15</v>
       </c>
       <c r="I8">
         <v>0.5</v>
@@ -694,16 +694,16 @@
         <v>Expansión</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-18</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-04</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-18</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-20</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -729,16 +729,16 @@
         <v>Expansión</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-06</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-25</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-07-26</v>
+        <v>2026-07-25</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -764,16 +764,16 @@
         <v>Expansión</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-09</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-25</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-29</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -799,16 +799,16 @@
         <v>Expansión</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-11</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-05-01</v>
+        <v>2026-04-30</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-06-12</v>
+        <v>2026-06-11</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-07-02</v>
+        <v>2026-07-01</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -834,16 +834,16 @@
         <v>Expansión</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-25</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-06</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-27</v>
+        <v>2026-08-26</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -869,16 +869,16 @@
         <v>Expansión</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-04</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-07-24</v>
+        <v>2026-07-23</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-04</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-23</v>
       </c>
       <c r="I14">
         <v>0.6</v>
@@ -904,16 +904,16 @@
         <v>Expansión</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-08-28</v>
+        <v>2026-08-27</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-01</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-28</v>
       </c>
       <c r="I15">
         <v>0.01</v>
@@ -939,16 +939,16 @@
         <v>Expansión</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-09-06</v>
+        <v>2026-09-05</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-09-25</v>
+        <v>2026-09-24</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-11-06</v>
+        <v>2026-11-05</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-11-26</v>
+        <v>2026-11-25</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -974,16 +974,16 @@
         <v>Expansión</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-03</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-22</v>
       </c>
       <c r="G17" t="str">
-        <v>2026-12-04</v>
+        <v>2026-12-03</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-12-24</v>
+        <v>2026-12-23</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1009,16 +1009,16 @@
         <v>Expansión</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-11-01</v>
+        <v>2026-10-31</v>
       </c>
       <c r="F18" t="str">
-        <v>2026-11-20</v>
+        <v>2026-11-19</v>
       </c>
       <c r="G18" t="str">
-        <v>2027-01-01</v>
+        <v>2026-12-31</v>
       </c>
       <c r="H18" t="str">
-        <v>2027-01-21</v>
+        <v>2027-01-20</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1044,16 +1044,16 @@
         <v>Expansión</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-11-29</v>
+        <v>2026-11-28</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-12-18</v>
+        <v>2026-12-17</v>
       </c>
       <c r="G19" t="str">
-        <v>2027-01-29</v>
+        <v>2027-01-28</v>
       </c>
       <c r="H19" t="str">
-        <v>2027-02-18</v>
+        <v>2027-02-17</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1079,16 +1079,16 @@
         <v>Expansión</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-12-27</v>
+        <v>2026-12-26</v>
       </c>
       <c r="F20" t="str">
-        <v>2027-01-22</v>
+        <v>2027-01-21</v>
       </c>
       <c r="G20" t="str">
-        <v>2027-02-27</v>
+        <v>2027-02-26</v>
       </c>
       <c r="H20" t="str">
-        <v>2027-03-25</v>
+        <v>2027-03-24</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1114,16 +1114,16 @@
         <v>Expansión</v>
       </c>
       <c r="E21" t="str">
-        <v>2027-01-31</v>
+        <v>2027-01-30</v>
       </c>
       <c r="F21" t="str">
-        <v>2027-02-19</v>
+        <v>2027-02-18</v>
       </c>
       <c r="G21" t="str">
-        <v>2027-03-31</v>
+        <v>2027-03-30</v>
       </c>
       <c r="H21" t="str">
-        <v>2027-04-21</v>
+        <v>2027-04-20</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1149,16 +1149,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-02</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-28</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-02</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-28</v>
       </c>
       <c r="I22">
         <v>0.5</v>
@@ -1184,16 +1184,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-04</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-07-31</v>
+        <v>2026-07-30</v>
       </c>
       <c r="G23" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-04</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-09-30</v>
+        <v>2026-09-29</v>
       </c>
       <c r="I23">
         <v>0.4</v>
@@ -1219,16 +1219,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-09</v>
+        <v>2026-08-08</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-09-11</v>
+        <v>2026-09-10</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-08-09</v>
+        <v>2026-08-08</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-11-11</v>
+        <v>2026-11-10</v>
       </c>
       <c r="I24">
         <v>0.1</v>
@@ -1254,16 +1254,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-19</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-10-16</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-19</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-12-16</v>
+        <v>2026-12-15</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1289,16 +1289,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-24</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-11-20</v>
+        <v>2026-11-19</v>
       </c>
       <c r="G26" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-24</v>
       </c>
       <c r="H26" t="str">
-        <v>2027-01-20</v>
+        <v>2027-01-19</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1324,16 +1324,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-11-29</v>
+        <v>2026-11-28</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-12-25</v>
+        <v>2026-12-24</v>
       </c>
       <c r="G27" t="str">
-        <v>2026-11-29</v>
+        <v>2026-11-28</v>
       </c>
       <c r="H27" t="str">
-        <v>2027-02-25</v>
+        <v>2027-02-24</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1359,16 +1359,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E28" t="str">
-        <v>2027-01-03</v>
+        <v>2027-01-02</v>
       </c>
       <c r="F28" t="str">
-        <v>2027-01-29</v>
+        <v>2027-01-28</v>
       </c>
       <c r="G28" t="str">
-        <v>2027-01-03</v>
+        <v>2027-01-02</v>
       </c>
       <c r="H28" t="str">
-        <v>2027-03-29</v>
+        <v>2027-03-28</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1394,16 +1394,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E29" t="str">
-        <v>2027-02-07</v>
+        <v>2027-02-06</v>
       </c>
       <c r="F29" t="str">
-        <v>2027-03-05</v>
+        <v>2027-03-04</v>
       </c>
       <c r="G29" t="str">
-        <v>2027-02-07</v>
+        <v>2027-02-06</v>
       </c>
       <c r="H29" t="str">
-        <v>2027-05-05</v>
+        <v>2027-05-04</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1429,16 +1429,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E30" t="str">
-        <v>2027-03-14</v>
+        <v>2027-03-13</v>
       </c>
       <c r="F30" t="str">
-        <v>2027-04-09</v>
+        <v>2027-04-08</v>
       </c>
       <c r="G30" t="str">
-        <v>2027-03-14</v>
+        <v>2027-03-13</v>
       </c>
       <c r="H30" t="str">
-        <v>2027-06-09</v>
+        <v>2027-06-08</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1464,16 +1464,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E31" t="str">
-        <v>2027-04-18</v>
+        <v>2027-04-17</v>
       </c>
       <c r="F31" t="str">
-        <v>2027-05-14</v>
+        <v>2027-05-13</v>
       </c>
       <c r="G31" t="str">
-        <v>2027-04-18</v>
+        <v>2027-04-17</v>
       </c>
       <c r="H31" t="str">
-        <v>2027-07-01</v>
+        <v>2027-06-30</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1499,16 +1499,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-05-31</v>
+        <v>2026-05-30</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-20</v>
       </c>
       <c r="G32" t="str">
-        <v>2026-07-31</v>
+        <v>2026-07-30</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-21</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-22</v>
       </c>
       <c r="G33" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-01</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-12-24</v>
+        <v>2026-12-23</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1569,16 +1569,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-12</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-12-04</v>
+        <v>2026-12-03</v>
       </c>
       <c r="G34" t="str">
-        <v>2026-11-13</v>
+        <v>2026-11-12</v>
       </c>
       <c r="H34" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-03</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1604,16 +1604,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-10-18</v>
+        <v>2026-10-17</v>
       </c>
       <c r="F35" t="str">
-        <v>2027-01-08</v>
+        <v>2027-01-07</v>
       </c>
       <c r="G35" t="str">
-        <v>2026-12-18</v>
+        <v>2026-12-17</v>
       </c>
       <c r="H35" t="str">
-        <v>2027-03-11</v>
+        <v>2027-03-10</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1639,16 +1639,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-11-22</v>
+        <v>2026-11-21</v>
       </c>
       <c r="F36" t="str">
-        <v>2027-02-12</v>
+        <v>2027-02-11</v>
       </c>
       <c r="G36" t="str">
-        <v>2027-01-22</v>
+        <v>2027-01-21</v>
       </c>
       <c r="H36" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-14</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1674,16 +1674,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-12-27</v>
+        <v>2026-12-26</v>
       </c>
       <c r="F37" t="str">
-        <v>2027-03-19</v>
+        <v>2027-03-18</v>
       </c>
       <c r="G37" t="str">
-        <v>2027-02-27</v>
+        <v>2027-02-26</v>
       </c>
       <c r="H37" t="str">
-        <v>2027-05-20</v>
+        <v>2027-05-19</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1709,16 +1709,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E38" t="str">
-        <v>2027-01-31</v>
+        <v>2027-01-30</v>
       </c>
       <c r="F38" t="str">
-        <v>2027-04-23</v>
+        <v>2027-04-22</v>
       </c>
       <c r="G38" t="str">
-        <v>2027-03-31</v>
+        <v>2027-03-30</v>
       </c>
       <c r="H38" t="str">
-        <v>2027-06-23</v>
+        <v>2027-06-22</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -1744,16 +1744,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E39" t="str">
-        <v>2027-03-07</v>
+        <v>2027-03-06</v>
       </c>
       <c r="F39" t="str">
-        <v>2027-05-28</v>
+        <v>2027-05-27</v>
       </c>
       <c r="G39" t="str">
-        <v>2027-05-07</v>
+        <v>2027-05-06</v>
       </c>
       <c r="H39" t="str">
-        <v>2027-07-29</v>
+        <v>2027-07-28</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -1779,16 +1779,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E40" t="str">
-        <v>2027-04-11</v>
+        <v>2027-04-10</v>
       </c>
       <c r="F40" t="str">
-        <v>2027-07-02</v>
+        <v>2027-07-01</v>
       </c>
       <c r="G40" t="str">
-        <v>2027-06-11</v>
+        <v>2027-06-10</v>
       </c>
       <c r="H40" t="str">
-        <v>2027-09-02</v>
+        <v>2027-09-01</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -1814,16 +1814,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E41" t="str">
-        <v>2027-05-16</v>
+        <v>2027-05-15</v>
       </c>
       <c r="F41" t="str">
-        <v>2027-08-06</v>
+        <v>2027-08-05</v>
       </c>
       <c r="G41" t="str">
-        <v>2027-07-16</v>
+        <v>2027-07-15</v>
       </c>
       <c r="H41" t="str">
-        <v>2027-10-07</v>
+        <v>2027-10-06</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>Obras</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-26</v>
+        <v>2026-07-25</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-11-13</v>
+        <v>2026-11-12</v>
       </c>
       <c r="G42" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-25</v>
       </c>
       <c r="H42" t="str">
-        <v>2027-01-14</v>
+        <v>2027-01-13</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -1884,16 +1884,16 @@
         <v>Obras</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-26</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-12-18</v>
+        <v>2026-12-17</v>
       </c>
       <c r="G43" t="str">
-        <v>2026-11-27</v>
+        <v>2026-11-26</v>
       </c>
       <c r="H43" t="str">
-        <v>2027-02-18</v>
+        <v>2027-02-17</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -1919,16 +1919,16 @@
         <v>Obras</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-11-08</v>
+        <v>2026-11-07</v>
       </c>
       <c r="F44" t="str">
-        <v>2027-02-26</v>
+        <v>2027-02-25</v>
       </c>
       <c r="G44" t="str">
-        <v>2027-01-08</v>
+        <v>2027-01-07</v>
       </c>
       <c r="H44" t="str">
-        <v>2027-04-29</v>
+        <v>2027-04-28</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -1954,16 +1954,16 @@
         <v>Obras</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-12-13</v>
+        <v>2026-12-12</v>
       </c>
       <c r="F45" t="str">
-        <v>2027-04-02</v>
+        <v>2027-04-01</v>
       </c>
       <c r="G45" t="str">
-        <v>2027-02-13</v>
+        <v>2027-02-12</v>
       </c>
       <c r="H45" t="str">
-        <v>2027-06-03</v>
+        <v>2027-06-02</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -1989,16 +1989,16 @@
         <v>Obras</v>
       </c>
       <c r="E46" t="str">
-        <v>2027-01-17</v>
+        <v>2027-01-16</v>
       </c>
       <c r="F46" t="str">
-        <v>2027-05-07</v>
+        <v>2027-05-06</v>
       </c>
       <c r="G46" t="str">
-        <v>2027-03-17</v>
+        <v>2027-03-16</v>
       </c>
       <c r="H46" t="str">
-        <v>2027-07-07</v>
+        <v>2027-07-06</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2024,16 +2024,16 @@
         <v>Obras</v>
       </c>
       <c r="E47" t="str">
-        <v>2027-02-21</v>
+        <v>2027-02-20</v>
       </c>
       <c r="F47" t="str">
-        <v>2027-06-11</v>
+        <v>2027-06-10</v>
       </c>
       <c r="G47" t="str">
-        <v>2027-04-21</v>
+        <v>2027-04-20</v>
       </c>
       <c r="H47" t="str">
-        <v>2027-08-11</v>
+        <v>2027-08-10</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2059,16 +2059,16 @@
         <v>Obras</v>
       </c>
       <c r="E48" t="str">
-        <v>2027-03-28</v>
+        <v>2027-03-27</v>
       </c>
       <c r="F48" t="str">
-        <v>2027-07-16</v>
+        <v>2027-07-15</v>
       </c>
       <c r="G48" t="str">
-        <v>2027-05-28</v>
+        <v>2027-05-27</v>
       </c>
       <c r="H48" t="str">
-        <v>2027-09-16</v>
+        <v>2027-09-15</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2094,16 +2094,16 @@
         <v>Obras</v>
       </c>
       <c r="E49" t="str">
-        <v>2027-05-02</v>
+        <v>2027-05-01</v>
       </c>
       <c r="F49" t="str">
-        <v>2027-08-20</v>
+        <v>2027-08-19</v>
       </c>
       <c r="G49" t="str">
-        <v>2027-07-02</v>
+        <v>2027-07-01</v>
       </c>
       <c r="H49" t="str">
-        <v>2027-10-21</v>
+        <v>2027-10-20</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2129,16 +2129,16 @@
         <v>Obras</v>
       </c>
       <c r="E50" t="str">
-        <v>2027-06-06</v>
+        <v>2027-06-05</v>
       </c>
       <c r="F50" t="str">
-        <v>2027-09-24</v>
+        <v>2027-09-23</v>
       </c>
       <c r="G50" t="str">
-        <v>2027-08-06</v>
+        <v>2027-08-05</v>
       </c>
       <c r="H50" t="str">
-        <v>2027-11-25</v>
+        <v>2027-11-24</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2164,16 +2164,16 @@
         <v>Obras</v>
       </c>
       <c r="E51" t="str">
-        <v>2027-07-11</v>
+        <v>2027-07-10</v>
       </c>
       <c r="F51" t="str">
-        <v>2027-10-29</v>
+        <v>2027-10-28</v>
       </c>
       <c r="G51" t="str">
-        <v>2027-09-11</v>
+        <v>2027-09-10</v>
       </c>
       <c r="H51" t="str">
-        <v>2027-12-30</v>
+        <v>2027-12-29</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2199,16 +2199,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-07-26</v>
+        <v>2026-07-25</v>
       </c>
       <c r="F52" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-17</v>
       </c>
       <c r="G52" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-25</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-11-19</v>
+        <v>2026-11-18</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2234,16 +2234,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-10-11</v>
+        <v>2026-10-10</v>
       </c>
       <c r="F53" t="str">
-        <v>2026-12-04</v>
+        <v>2026-12-03</v>
       </c>
       <c r="G53" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-10</v>
       </c>
       <c r="H53" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-03</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2269,16 +2269,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-11-08</v>
+        <v>2026-11-07</v>
       </c>
       <c r="F54" t="str">
-        <v>2027-01-01</v>
+        <v>2026-12-31</v>
       </c>
       <c r="G54" t="str">
-        <v>2027-01-08</v>
+        <v>2027-01-07</v>
       </c>
       <c r="H54" t="str">
-        <v>2027-03-04</v>
+        <v>2027-03-03</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2304,16 +2304,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-12-13</v>
+        <v>2026-12-12</v>
       </c>
       <c r="F55" t="str">
-        <v>2027-02-05</v>
+        <v>2027-02-04</v>
       </c>
       <c r="G55" t="str">
-        <v>2027-02-13</v>
+        <v>2027-02-12</v>
       </c>
       <c r="H55" t="str">
-        <v>2027-04-08</v>
+        <v>2027-04-07</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2339,16 +2339,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E56" t="str">
-        <v>2027-01-17</v>
+        <v>2027-01-16</v>
       </c>
       <c r="F56" t="str">
-        <v>2027-03-12</v>
+        <v>2027-03-11</v>
       </c>
       <c r="G56" t="str">
-        <v>2027-03-17</v>
+        <v>2027-03-16</v>
       </c>
       <c r="H56" t="str">
-        <v>2027-05-12</v>
+        <v>2027-05-11</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2374,16 +2374,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E57" t="str">
-        <v>2027-02-21</v>
+        <v>2027-02-20</v>
       </c>
       <c r="F57" t="str">
-        <v>2027-04-16</v>
+        <v>2027-04-15</v>
       </c>
       <c r="G57" t="str">
-        <v>2027-04-21</v>
+        <v>2027-04-20</v>
       </c>
       <c r="H57" t="str">
-        <v>2027-06-16</v>
+        <v>2027-06-15</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2409,16 +2409,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E58" t="str">
-        <v>2027-03-28</v>
+        <v>2027-03-27</v>
       </c>
       <c r="F58" t="str">
-        <v>2027-05-21</v>
+        <v>2027-05-20</v>
       </c>
       <c r="G58" t="str">
-        <v>2027-05-28</v>
+        <v>2027-05-27</v>
       </c>
       <c r="H58" t="str">
-        <v>2027-07-22</v>
+        <v>2027-07-21</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2444,16 +2444,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E59" t="str">
-        <v>2027-05-02</v>
+        <v>2027-05-01</v>
       </c>
       <c r="F59" t="str">
-        <v>2027-06-25</v>
+        <v>2027-06-24</v>
       </c>
       <c r="G59" t="str">
-        <v>2027-07-02</v>
+        <v>2027-07-01</v>
       </c>
       <c r="H59" t="str">
-        <v>2027-08-26</v>
+        <v>2027-08-25</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2479,16 +2479,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E60" t="str">
-        <v>2027-06-06</v>
+        <v>2027-06-05</v>
       </c>
       <c r="F60" t="str">
-        <v>2027-07-30</v>
+        <v>2027-07-29</v>
       </c>
       <c r="G60" t="str">
-        <v>2027-08-06</v>
+        <v>2027-08-05</v>
       </c>
       <c r="H60" t="str">
-        <v>2027-09-30</v>
+        <v>2027-09-29</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2514,16 +2514,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E61" t="str">
-        <v>2027-07-11</v>
+        <v>2027-07-10</v>
       </c>
       <c r="F61" t="str">
-        <v>2027-09-03</v>
+        <v>2027-09-02</v>
       </c>
       <c r="G61" t="str">
-        <v>2027-09-11</v>
+        <v>2027-09-10</v>
       </c>
       <c r="H61" t="str">
-        <v>2027-11-04</v>
+        <v>2027-11-03</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2549,16 +2549,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-19</v>
       </c>
       <c r="F62" t="str">
-        <v>2026-11-13</v>
+        <v>2026-11-12</v>
       </c>
       <c r="G62" t="str">
-        <v>2026-11-20</v>
+        <v>2026-11-19</v>
       </c>
       <c r="H62" t="str">
-        <v>2027-01-14</v>
+        <v>2027-01-13</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2584,16 +2584,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-12-06</v>
+        <v>2026-12-05</v>
       </c>
       <c r="F63" t="str">
-        <v>2027-01-29</v>
+        <v>2027-01-28</v>
       </c>
       <c r="G63" t="str">
-        <v>2027-02-06</v>
+        <v>2027-02-05</v>
       </c>
       <c r="H63" t="str">
-        <v>2027-04-01</v>
+        <v>2027-03-31</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2619,16 +2619,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E64" t="str">
-        <v>2027-01-03</v>
+        <v>2027-01-02</v>
       </c>
       <c r="F64" t="str">
-        <v>2027-02-26</v>
+        <v>2027-02-25</v>
       </c>
       <c r="G64" t="str">
-        <v>2027-03-03</v>
+        <v>2027-03-02</v>
       </c>
       <c r="H64" t="str">
-        <v>2027-04-28</v>
+        <v>2027-04-27</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E65" t="str">
-        <v>2027-02-07</v>
+        <v>2027-02-06</v>
       </c>
       <c r="F65" t="str">
-        <v>2027-04-02</v>
+        <v>2027-04-01</v>
       </c>
       <c r="G65" t="str">
-        <v>2027-04-07</v>
+        <v>2027-04-06</v>
       </c>
       <c r="H65" t="str">
-        <v>2027-06-02</v>
+        <v>2027-06-01</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2689,16 +2689,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E66" t="str">
-        <v>2027-03-14</v>
+        <v>2027-03-13</v>
       </c>
       <c r="F66" t="str">
-        <v>2027-05-07</v>
+        <v>2027-05-06</v>
       </c>
       <c r="G66" t="str">
-        <v>2027-05-14</v>
+        <v>2027-05-13</v>
       </c>
       <c r="H66" t="str">
-        <v>2027-07-08</v>
+        <v>2027-07-07</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -2724,16 +2724,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E67" t="str">
-        <v>2027-04-18</v>
+        <v>2027-04-17</v>
       </c>
       <c r="F67" t="str">
-        <v>2027-06-11</v>
+        <v>2027-06-10</v>
       </c>
       <c r="G67" t="str">
-        <v>2027-06-18</v>
+        <v>2027-06-17</v>
       </c>
       <c r="H67" t="str">
-        <v>2027-08-12</v>
+        <v>2027-08-11</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2759,16 +2759,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E68" t="str">
-        <v>2027-05-23</v>
+        <v>2027-05-22</v>
       </c>
       <c r="F68" t="str">
-        <v>2027-07-16</v>
+        <v>2027-07-15</v>
       </c>
       <c r="G68" t="str">
-        <v>2027-07-23</v>
+        <v>2027-07-22</v>
       </c>
       <c r="H68" t="str">
-        <v>2027-09-16</v>
+        <v>2027-09-15</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -2794,16 +2794,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E69" t="str">
-        <v>2027-06-27</v>
+        <v>2027-06-26</v>
       </c>
       <c r="F69" t="str">
-        <v>2027-08-20</v>
+        <v>2027-08-19</v>
       </c>
       <c r="G69" t="str">
-        <v>2027-08-27</v>
+        <v>2027-08-26</v>
       </c>
       <c r="H69" t="str">
-        <v>2027-10-21</v>
+        <v>2027-10-20</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -2829,16 +2829,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E70" t="str">
-        <v>2027-08-01</v>
+        <v>2027-07-31</v>
       </c>
       <c r="F70" t="str">
-        <v>2027-09-24</v>
+        <v>2027-09-23</v>
       </c>
       <c r="G70" t="str">
-        <v>2027-10-01</v>
+        <v>2027-09-30</v>
       </c>
       <c r="H70" t="str">
-        <v>2027-11-25</v>
+        <v>2027-11-24</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -2864,16 +2864,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E71" t="str">
-        <v>2027-09-05</v>
+        <v>2027-09-04</v>
       </c>
       <c r="F71" t="str">
-        <v>2027-10-29</v>
+        <v>2027-10-28</v>
       </c>
       <c r="G71" t="str">
-        <v>2027-11-05</v>
+        <v>2027-11-04</v>
       </c>
       <c r="H71" t="str">
-        <v>2027-12-30</v>
+        <v>2027-12-29</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -2899,16 +2899,16 @@
         <v>Dirección</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-11-29</v>
+        <v>2026-11-28</v>
       </c>
       <c r="F72" t="str">
-        <v>2026-11-29</v>
+        <v>2026-11-28</v>
       </c>
       <c r="G72" t="str">
-        <v>2027-01-31</v>
+        <v>2027-01-30</v>
       </c>
       <c r="H72" t="str">
-        <v>2027-01-31</v>
+        <v>2027-01-30</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -2934,16 +2934,16 @@
         <v>Dirección</v>
       </c>
       <c r="E73" t="str">
-        <v>2027-02-14</v>
+        <v>2027-02-13</v>
       </c>
       <c r="F73" t="str">
-        <v>2027-02-14</v>
+        <v>2027-02-13</v>
       </c>
       <c r="G73" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-13</v>
       </c>
       <c r="H73" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-13</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -2969,16 +2969,16 @@
         <v>Dirección</v>
       </c>
       <c r="E74" t="str">
-        <v>2027-03-14</v>
+        <v>2027-03-13</v>
       </c>
       <c r="F74" t="str">
-        <v>2027-03-14</v>
+        <v>2027-03-13</v>
       </c>
       <c r="G74" t="str">
-        <v>2027-05-14</v>
+        <v>2027-05-13</v>
       </c>
       <c r="H74" t="str">
-        <v>2027-05-14</v>
+        <v>2027-05-13</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3004,16 +3004,16 @@
         <v>Dirección</v>
       </c>
       <c r="E75" t="str">
-        <v>2027-04-18</v>
+        <v>2027-04-17</v>
       </c>
       <c r="F75" t="str">
-        <v>2027-04-18</v>
+        <v>2027-04-17</v>
       </c>
       <c r="G75" t="str">
-        <v>2027-06-18</v>
+        <v>2027-06-17</v>
       </c>
       <c r="H75" t="str">
-        <v>2027-06-18</v>
+        <v>2027-06-17</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3039,16 +3039,16 @@
         <v>Dirección</v>
       </c>
       <c r="E76" t="str">
-        <v>2027-05-23</v>
+        <v>2027-05-22</v>
       </c>
       <c r="F76" t="str">
-        <v>2027-05-23</v>
+        <v>2027-05-22</v>
       </c>
       <c r="G76" t="str">
-        <v>2027-07-23</v>
+        <v>2027-07-22</v>
       </c>
       <c r="H76" t="str">
-        <v>2027-07-23</v>
+        <v>2027-07-22</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3074,16 +3074,16 @@
         <v>Dirección</v>
       </c>
       <c r="E77" t="str">
-        <v>2027-06-27</v>
+        <v>2027-06-26</v>
       </c>
       <c r="F77" t="str">
-        <v>2027-06-27</v>
+        <v>2027-06-26</v>
       </c>
       <c r="G77" t="str">
-        <v>2027-08-27</v>
+        <v>2027-08-26</v>
       </c>
       <c r="H77" t="str">
-        <v>2027-08-27</v>
+        <v>2027-08-26</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3109,16 +3109,16 @@
         <v>Dirección</v>
       </c>
       <c r="E78" t="str">
-        <v>2027-08-01</v>
+        <v>2027-07-31</v>
       </c>
       <c r="F78" t="str">
-        <v>2027-08-01</v>
+        <v>2027-07-31</v>
       </c>
       <c r="G78" t="str">
-        <v>2027-10-01</v>
+        <v>2027-09-30</v>
       </c>
       <c r="H78" t="str">
-        <v>2027-10-01</v>
+        <v>2027-09-30</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3144,16 +3144,16 @@
         <v>Dirección</v>
       </c>
       <c r="E79" t="str">
-        <v>2027-09-04</v>
+        <v>2027-09-03</v>
       </c>
       <c r="F79" t="str">
-        <v>2027-09-04</v>
+        <v>2027-09-03</v>
       </c>
       <c r="G79" t="str">
-        <v>2027-11-04</v>
+        <v>2027-11-03</v>
       </c>
       <c r="H79" t="str">
-        <v>2027-11-04</v>
+        <v>2027-11-03</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3179,16 +3179,16 @@
         <v>Dirección</v>
       </c>
       <c r="E80" t="str">
-        <v>2027-10-10</v>
+        <v>2027-10-09</v>
       </c>
       <c r="F80" t="str">
-        <v>2027-10-10</v>
+        <v>2027-10-09</v>
       </c>
       <c r="G80" t="str">
-        <v>2027-12-10</v>
+        <v>2027-12-09</v>
       </c>
       <c r="H80" t="str">
-        <v>2027-12-10</v>
+        <v>2027-12-09</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3214,16 +3214,16 @@
         <v>Dirección</v>
       </c>
       <c r="E81" t="str">
-        <v>2027-11-14</v>
+        <v>2027-11-13</v>
       </c>
       <c r="F81" t="str">
-        <v>2027-11-14</v>
+        <v>2027-11-13</v>
       </c>
       <c r="G81" t="str">
-        <v>2028-01-14</v>
+        <v>2028-01-13</v>
       </c>
       <c r="H81" t="str">
-        <v>2028-01-14</v>
+        <v>2028-01-13</v>
       </c>
       <c r="I81">
         <v>0</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -449,22 +449,22 @@
         <v>Expansión</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-03-30</v>
+        <v>2026-03-29</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-17</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-03-30</v>
+        <v>2026-03-29</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="I2">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="J2" t="str">
-        <v>En progreso</v>
+        <v>Completado</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -484,16 +484,16 @@
         <v>Expansión</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-03-30</v>
+        <v>2026-03-29</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-19</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-03-30</v>
+        <v>2026-03-29</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -519,16 +519,16 @@
         <v>Expansión</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-03</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-21</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-03</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-03</v>
       </c>
       <c r="I4">
         <v>0.5</v>
@@ -554,16 +554,16 @@
         <v>Expansión</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-03</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-24</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-03</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-24</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -589,16 +589,16 @@
         <v>Expansión</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-26</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-10</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-07-08</v>
+        <v>2026-07-07</v>
       </c>
       <c r="I6">
         <v>0.5</v>
@@ -624,16 +624,16 @@
         <v>Expansión</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-10</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-07-12</v>
+        <v>2026-07-11</v>
       </c>
       <c r="I7">
         <v>0.5</v>
@@ -659,16 +659,16 @@
         <v>Expansión</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-17</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-01</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-17</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-14</v>
       </c>
       <c r="I8">
         <v>0.5</v>
@@ -694,16 +694,16 @@
         <v>Expansión</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-17</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-03</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-17</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-07-20</v>
+        <v>2026-07-19</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -729,16 +729,16 @@
         <v>Expansión</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-24</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-05</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-24</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-07-25</v>
+        <v>2026-07-24</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -764,16 +764,16 @@
         <v>Expansión</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-24</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-08</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-24</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-28</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -799,16 +799,16 @@
         <v>Expansión</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-04-30</v>
+        <v>2026-04-29</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-06-11</v>
+        <v>2026-06-10</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-07-01</v>
+        <v>2026-06-30</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -834,16 +834,16 @@
         <v>Expansión</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-06-25</v>
+        <v>2026-06-24</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-05</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-26</v>
+        <v>2026-08-25</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -869,16 +869,16 @@
         <v>Expansión</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-03</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-07-23</v>
+        <v>2026-07-22</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-09-04</v>
+        <v>2026-09-03</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-22</v>
       </c>
       <c r="I14">
         <v>0.6</v>
@@ -904,16 +904,16 @@
         <v>Expansión</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-31</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-08-27</v>
+        <v>2026-08-26</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-30</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-27</v>
       </c>
       <c r="I15">
         <v>0.01</v>
@@ -939,16 +939,16 @@
         <v>Expansión</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-04</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-23</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-11-05</v>
+        <v>2026-11-04</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-11-25</v>
+        <v>2026-11-24</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -974,16 +974,16 @@
         <v>Expansión</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-02</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G17" t="str">
-        <v>2026-12-03</v>
+        <v>2026-12-02</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-12-23</v>
+        <v>2026-12-22</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1009,16 +1009,16 @@
         <v>Expansión</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-10-31</v>
+        <v>2026-10-30</v>
       </c>
       <c r="F18" t="str">
-        <v>2026-11-19</v>
+        <v>2026-11-18</v>
       </c>
       <c r="G18" t="str">
-        <v>2026-12-31</v>
+        <v>2026-12-30</v>
       </c>
       <c r="H18" t="str">
-        <v>2027-01-20</v>
+        <v>2027-01-19</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1044,16 +1044,16 @@
         <v>Expansión</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-11-28</v>
+        <v>2026-11-27</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-12-17</v>
+        <v>2026-12-16</v>
       </c>
       <c r="G19" t="str">
-        <v>2027-01-28</v>
+        <v>2027-01-27</v>
       </c>
       <c r="H19" t="str">
-        <v>2027-02-17</v>
+        <v>2027-02-16</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1079,16 +1079,16 @@
         <v>Expansión</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-12-26</v>
+        <v>2026-12-25</v>
       </c>
       <c r="F20" t="str">
-        <v>2027-01-21</v>
+        <v>2027-01-20</v>
       </c>
       <c r="G20" t="str">
-        <v>2027-02-26</v>
+        <v>2027-02-25</v>
       </c>
       <c r="H20" t="str">
-        <v>2027-03-24</v>
+        <v>2027-03-23</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1114,16 +1114,16 @@
         <v>Expansión</v>
       </c>
       <c r="E21" t="str">
-        <v>2027-01-30</v>
+        <v>2027-01-29</v>
       </c>
       <c r="F21" t="str">
-        <v>2027-02-18</v>
+        <v>2027-02-17</v>
       </c>
       <c r="G21" t="str">
-        <v>2027-03-30</v>
+        <v>2027-03-29</v>
       </c>
       <c r="H21" t="str">
-        <v>2027-04-20</v>
+        <v>2027-04-19</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1149,16 +1149,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-01</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-27</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-01</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-27</v>
       </c>
       <c r="I22">
         <v>0.5</v>
@@ -1184,16 +1184,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-03</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-29</v>
       </c>
       <c r="G23" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-03</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="I23">
         <v>0.4</v>
@@ -1219,16 +1219,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-07</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-09-10</v>
+        <v>2026-09-09</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-07</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-11-10</v>
+        <v>2026-11-09</v>
       </c>
       <c r="I24">
         <v>0.1</v>
@@ -1254,16 +1254,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-18</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-14</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-18</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-12-15</v>
+        <v>2026-12-14</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1289,16 +1289,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-23</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-11-19</v>
+        <v>2026-11-18</v>
       </c>
       <c r="G26" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-23</v>
       </c>
       <c r="H26" t="str">
-        <v>2027-01-19</v>
+        <v>2027-01-18</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1324,16 +1324,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-11-28</v>
+        <v>2026-11-27</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-12-24</v>
+        <v>2026-12-23</v>
       </c>
       <c r="G27" t="str">
-        <v>2026-11-28</v>
+        <v>2026-11-27</v>
       </c>
       <c r="H27" t="str">
-        <v>2027-02-24</v>
+        <v>2027-02-23</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1359,16 +1359,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E28" t="str">
-        <v>2027-01-02</v>
+        <v>2027-01-01</v>
       </c>
       <c r="F28" t="str">
-        <v>2027-01-28</v>
+        <v>2027-01-27</v>
       </c>
       <c r="G28" t="str">
-        <v>2027-01-02</v>
+        <v>2027-01-01</v>
       </c>
       <c r="H28" t="str">
-        <v>2027-03-28</v>
+        <v>2027-03-27</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1394,16 +1394,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E29" t="str">
-        <v>2027-02-06</v>
+        <v>2027-02-05</v>
       </c>
       <c r="F29" t="str">
-        <v>2027-03-04</v>
+        <v>2027-03-03</v>
       </c>
       <c r="G29" t="str">
-        <v>2027-02-06</v>
+        <v>2027-02-05</v>
       </c>
       <c r="H29" t="str">
-        <v>2027-05-04</v>
+        <v>2027-05-03</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1429,16 +1429,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E30" t="str">
-        <v>2027-03-13</v>
+        <v>2027-03-12</v>
       </c>
       <c r="F30" t="str">
-        <v>2027-04-08</v>
+        <v>2027-04-07</v>
       </c>
       <c r="G30" t="str">
-        <v>2027-03-13</v>
+        <v>2027-03-12</v>
       </c>
       <c r="H30" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-07</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1464,16 +1464,16 @@
         <v>Expansión / Jurídico</v>
       </c>
       <c r="E31" t="str">
-        <v>2027-04-17</v>
+        <v>2027-04-16</v>
       </c>
       <c r="F31" t="str">
-        <v>2027-05-13</v>
+        <v>2027-05-12</v>
       </c>
       <c r="G31" t="str">
-        <v>2027-04-17</v>
+        <v>2027-04-16</v>
       </c>
       <c r="H31" t="str">
-        <v>2027-06-30</v>
+        <v>2027-06-29</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1499,16 +1499,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-29</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-08-20</v>
+        <v>2026-08-19</v>
       </c>
       <c r="G32" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-29</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-20</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-31</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G33" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-30</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-12-23</v>
+        <v>2026-12-22</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1569,16 +1569,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-09-12</v>
+        <v>2026-09-11</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-12-03</v>
+        <v>2026-12-02</v>
       </c>
       <c r="G34" t="str">
-        <v>2026-11-12</v>
+        <v>2026-11-11</v>
       </c>
       <c r="H34" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-02</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1604,16 +1604,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-10-17</v>
+        <v>2026-10-16</v>
       </c>
       <c r="F35" t="str">
-        <v>2027-01-07</v>
+        <v>2027-01-06</v>
       </c>
       <c r="G35" t="str">
-        <v>2026-12-17</v>
+        <v>2026-12-16</v>
       </c>
       <c r="H35" t="str">
-        <v>2027-03-10</v>
+        <v>2027-03-09</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1639,16 +1639,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-11-21</v>
+        <v>2026-11-20</v>
       </c>
       <c r="F36" t="str">
-        <v>2027-02-11</v>
+        <v>2027-02-10</v>
       </c>
       <c r="G36" t="str">
-        <v>2027-01-21</v>
+        <v>2027-01-20</v>
       </c>
       <c r="H36" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-13</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1674,16 +1674,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-12-26</v>
+        <v>2026-12-25</v>
       </c>
       <c r="F37" t="str">
-        <v>2027-03-18</v>
+        <v>2027-03-17</v>
       </c>
       <c r="G37" t="str">
-        <v>2027-02-26</v>
+        <v>2027-02-25</v>
       </c>
       <c r="H37" t="str">
-        <v>2027-05-19</v>
+        <v>2027-05-18</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1709,16 +1709,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E38" t="str">
-        <v>2027-01-30</v>
+        <v>2027-01-29</v>
       </c>
       <c r="F38" t="str">
-        <v>2027-04-22</v>
+        <v>2027-04-21</v>
       </c>
       <c r="G38" t="str">
-        <v>2027-03-30</v>
+        <v>2027-03-29</v>
       </c>
       <c r="H38" t="str">
-        <v>2027-06-22</v>
+        <v>2027-06-21</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -1744,16 +1744,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E39" t="str">
-        <v>2027-03-06</v>
+        <v>2027-03-05</v>
       </c>
       <c r="F39" t="str">
-        <v>2027-05-27</v>
+        <v>2027-05-26</v>
       </c>
       <c r="G39" t="str">
-        <v>2027-05-06</v>
+        <v>2027-05-05</v>
       </c>
       <c r="H39" t="str">
-        <v>2027-07-28</v>
+        <v>2027-07-27</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -1779,16 +1779,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E40" t="str">
-        <v>2027-04-10</v>
+        <v>2027-04-09</v>
       </c>
       <c r="F40" t="str">
-        <v>2027-07-01</v>
+        <v>2027-06-30</v>
       </c>
       <c r="G40" t="str">
-        <v>2027-06-10</v>
+        <v>2027-06-09</v>
       </c>
       <c r="H40" t="str">
-        <v>2027-09-01</v>
+        <v>2027-08-31</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -1814,16 +1814,16 @@
         <v>Jurídico / Obras</v>
       </c>
       <c r="E41" t="str">
-        <v>2027-05-15</v>
+        <v>2027-05-14</v>
       </c>
       <c r="F41" t="str">
-        <v>2027-08-05</v>
+        <v>2027-08-04</v>
       </c>
       <c r="G41" t="str">
-        <v>2027-07-15</v>
+        <v>2027-07-14</v>
       </c>
       <c r="H41" t="str">
-        <v>2027-10-06</v>
+        <v>2027-10-05</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>Obras</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-25</v>
+        <v>2026-07-24</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-11-12</v>
+        <v>2026-11-11</v>
       </c>
       <c r="G42" t="str">
-        <v>2026-09-25</v>
+        <v>2026-09-24</v>
       </c>
       <c r="H42" t="str">
-        <v>2027-01-13</v>
+        <v>2027-01-12</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -1884,16 +1884,16 @@
         <v>Obras</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-25</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-12-17</v>
+        <v>2026-12-16</v>
       </c>
       <c r="G43" t="str">
-        <v>2026-11-26</v>
+        <v>2026-11-25</v>
       </c>
       <c r="H43" t="str">
-        <v>2027-02-17</v>
+        <v>2027-02-16</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -1919,16 +1919,16 @@
         <v>Obras</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-11-07</v>
+        <v>2026-11-06</v>
       </c>
       <c r="F44" t="str">
-        <v>2027-02-25</v>
+        <v>2027-02-24</v>
       </c>
       <c r="G44" t="str">
-        <v>2027-01-07</v>
+        <v>2027-01-06</v>
       </c>
       <c r="H44" t="str">
-        <v>2027-04-28</v>
+        <v>2027-04-27</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -1954,16 +1954,16 @@
         <v>Obras</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-12-12</v>
+        <v>2026-12-11</v>
       </c>
       <c r="F45" t="str">
-        <v>2027-04-01</v>
+        <v>2027-03-31</v>
       </c>
       <c r="G45" t="str">
-        <v>2027-02-12</v>
+        <v>2027-02-11</v>
       </c>
       <c r="H45" t="str">
-        <v>2027-06-02</v>
+        <v>2027-06-01</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -1989,16 +1989,16 @@
         <v>Obras</v>
       </c>
       <c r="E46" t="str">
-        <v>2027-01-16</v>
+        <v>2027-01-15</v>
       </c>
       <c r="F46" t="str">
-        <v>2027-05-06</v>
+        <v>2027-05-05</v>
       </c>
       <c r="G46" t="str">
-        <v>2027-03-16</v>
+        <v>2027-03-15</v>
       </c>
       <c r="H46" t="str">
-        <v>2027-07-06</v>
+        <v>2027-07-05</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2024,16 +2024,16 @@
         <v>Obras</v>
       </c>
       <c r="E47" t="str">
-        <v>2027-02-20</v>
+        <v>2027-02-19</v>
       </c>
       <c r="F47" t="str">
-        <v>2027-06-10</v>
+        <v>2027-06-09</v>
       </c>
       <c r="G47" t="str">
-        <v>2027-04-20</v>
+        <v>2027-04-19</v>
       </c>
       <c r="H47" t="str">
-        <v>2027-08-10</v>
+        <v>2027-08-09</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2059,16 +2059,16 @@
         <v>Obras</v>
       </c>
       <c r="E48" t="str">
-        <v>2027-03-27</v>
+        <v>2027-03-26</v>
       </c>
       <c r="F48" t="str">
-        <v>2027-07-15</v>
+        <v>2027-07-14</v>
       </c>
       <c r="G48" t="str">
-        <v>2027-05-27</v>
+        <v>2027-05-26</v>
       </c>
       <c r="H48" t="str">
-        <v>2027-09-15</v>
+        <v>2027-09-14</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2094,16 +2094,16 @@
         <v>Obras</v>
       </c>
       <c r="E49" t="str">
-        <v>2027-05-01</v>
+        <v>2027-04-30</v>
       </c>
       <c r="F49" t="str">
-        <v>2027-08-19</v>
+        <v>2027-08-18</v>
       </c>
       <c r="G49" t="str">
-        <v>2027-07-01</v>
+        <v>2027-06-30</v>
       </c>
       <c r="H49" t="str">
-        <v>2027-10-20</v>
+        <v>2027-10-19</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2129,16 +2129,16 @@
         <v>Obras</v>
       </c>
       <c r="E50" t="str">
-        <v>2027-06-05</v>
+        <v>2027-06-04</v>
       </c>
       <c r="F50" t="str">
-        <v>2027-09-23</v>
+        <v>2027-09-22</v>
       </c>
       <c r="G50" t="str">
-        <v>2027-08-05</v>
+        <v>2027-08-04</v>
       </c>
       <c r="H50" t="str">
-        <v>2027-11-24</v>
+        <v>2027-11-23</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2164,16 +2164,16 @@
         <v>Obras</v>
       </c>
       <c r="E51" t="str">
-        <v>2027-07-10</v>
+        <v>2027-07-09</v>
       </c>
       <c r="F51" t="str">
-        <v>2027-10-28</v>
+        <v>2027-10-27</v>
       </c>
       <c r="G51" t="str">
-        <v>2027-09-10</v>
+        <v>2027-09-09</v>
       </c>
       <c r="H51" t="str">
-        <v>2027-12-29</v>
+        <v>2027-12-28</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2199,16 +2199,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-07-25</v>
+        <v>2026-07-24</v>
       </c>
       <c r="F52" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-16</v>
       </c>
       <c r="G52" t="str">
-        <v>2026-09-25</v>
+        <v>2026-09-24</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-11-18</v>
+        <v>2026-11-17</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2234,16 +2234,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-10-10</v>
+        <v>2026-10-09</v>
       </c>
       <c r="F53" t="str">
-        <v>2026-12-03</v>
+        <v>2026-12-02</v>
       </c>
       <c r="G53" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H53" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-02</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2269,16 +2269,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-11-07</v>
+        <v>2026-11-06</v>
       </c>
       <c r="F54" t="str">
-        <v>2026-12-31</v>
+        <v>2026-12-30</v>
       </c>
       <c r="G54" t="str">
-        <v>2027-01-07</v>
+        <v>2027-01-06</v>
       </c>
       <c r="H54" t="str">
-        <v>2027-03-03</v>
+        <v>2027-03-02</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2304,16 +2304,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-12-12</v>
+        <v>2026-12-11</v>
       </c>
       <c r="F55" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-03</v>
       </c>
       <c r="G55" t="str">
-        <v>2027-02-12</v>
+        <v>2027-02-11</v>
       </c>
       <c r="H55" t="str">
-        <v>2027-04-07</v>
+        <v>2027-04-06</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2339,16 +2339,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E56" t="str">
-        <v>2027-01-16</v>
+        <v>2027-01-15</v>
       </c>
       <c r="F56" t="str">
-        <v>2027-03-11</v>
+        <v>2027-03-10</v>
       </c>
       <c r="G56" t="str">
-        <v>2027-03-16</v>
+        <v>2027-03-15</v>
       </c>
       <c r="H56" t="str">
-        <v>2027-05-11</v>
+        <v>2027-05-10</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2374,16 +2374,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E57" t="str">
-        <v>2027-02-20</v>
+        <v>2027-02-19</v>
       </c>
       <c r="F57" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-14</v>
       </c>
       <c r="G57" t="str">
-        <v>2027-04-20</v>
+        <v>2027-04-19</v>
       </c>
       <c r="H57" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-14</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2409,16 +2409,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E58" t="str">
-        <v>2027-03-27</v>
+        <v>2027-03-26</v>
       </c>
       <c r="F58" t="str">
-        <v>2027-05-20</v>
+        <v>2027-05-19</v>
       </c>
       <c r="G58" t="str">
-        <v>2027-05-27</v>
+        <v>2027-05-26</v>
       </c>
       <c r="H58" t="str">
-        <v>2027-07-21</v>
+        <v>2027-07-20</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2444,16 +2444,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E59" t="str">
-        <v>2027-05-01</v>
+        <v>2027-04-30</v>
       </c>
       <c r="F59" t="str">
-        <v>2027-06-24</v>
+        <v>2027-06-23</v>
       </c>
       <c r="G59" t="str">
-        <v>2027-07-01</v>
+        <v>2027-06-30</v>
       </c>
       <c r="H59" t="str">
-        <v>2027-08-25</v>
+        <v>2027-08-24</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2479,16 +2479,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E60" t="str">
-        <v>2027-06-05</v>
+        <v>2027-06-04</v>
       </c>
       <c r="F60" t="str">
-        <v>2027-07-29</v>
+        <v>2027-07-28</v>
       </c>
       <c r="G60" t="str">
-        <v>2027-08-05</v>
+        <v>2027-08-04</v>
       </c>
       <c r="H60" t="str">
-        <v>2027-09-29</v>
+        <v>2027-09-28</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2514,16 +2514,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E61" t="str">
-        <v>2027-07-10</v>
+        <v>2027-07-09</v>
       </c>
       <c r="F61" t="str">
-        <v>2027-09-02</v>
+        <v>2027-09-01</v>
       </c>
       <c r="G61" t="str">
-        <v>2027-09-10</v>
+        <v>2027-09-09</v>
       </c>
       <c r="H61" t="str">
-        <v>2027-11-03</v>
+        <v>2027-11-02</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2549,16 +2549,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-18</v>
       </c>
       <c r="F62" t="str">
-        <v>2026-11-12</v>
+        <v>2026-11-11</v>
       </c>
       <c r="G62" t="str">
-        <v>2026-11-19</v>
+        <v>2026-11-18</v>
       </c>
       <c r="H62" t="str">
-        <v>2027-01-13</v>
+        <v>2027-01-12</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2584,16 +2584,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-12-05</v>
+        <v>2026-12-04</v>
       </c>
       <c r="F63" t="str">
-        <v>2027-01-28</v>
+        <v>2027-01-27</v>
       </c>
       <c r="G63" t="str">
-        <v>2027-02-05</v>
+        <v>2027-02-04</v>
       </c>
       <c r="H63" t="str">
-        <v>2027-03-31</v>
+        <v>2027-03-30</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2619,16 +2619,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E64" t="str">
-        <v>2027-01-02</v>
+        <v>2027-01-01</v>
       </c>
       <c r="F64" t="str">
-        <v>2027-02-25</v>
+        <v>2027-02-24</v>
       </c>
       <c r="G64" t="str">
-        <v>2027-03-02</v>
+        <v>2027-03-01</v>
       </c>
       <c r="H64" t="str">
-        <v>2027-04-27</v>
+        <v>2027-04-26</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E65" t="str">
-        <v>2027-02-06</v>
+        <v>2027-02-05</v>
       </c>
       <c r="F65" t="str">
-        <v>2027-04-01</v>
+        <v>2027-03-31</v>
       </c>
       <c r="G65" t="str">
-        <v>2027-04-06</v>
+        <v>2027-04-05</v>
       </c>
       <c r="H65" t="str">
-        <v>2027-06-01</v>
+        <v>2027-05-31</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2689,16 +2689,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E66" t="str">
-        <v>2027-03-13</v>
+        <v>2027-03-12</v>
       </c>
       <c r="F66" t="str">
-        <v>2027-05-06</v>
+        <v>2027-05-05</v>
       </c>
       <c r="G66" t="str">
-        <v>2027-05-13</v>
+        <v>2027-05-12</v>
       </c>
       <c r="H66" t="str">
-        <v>2027-07-07</v>
+        <v>2027-07-06</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -2724,16 +2724,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E67" t="str">
-        <v>2027-04-17</v>
+        <v>2027-04-16</v>
       </c>
       <c r="F67" t="str">
-        <v>2027-06-10</v>
+        <v>2027-06-09</v>
       </c>
       <c r="G67" t="str">
-        <v>2027-06-17</v>
+        <v>2027-06-16</v>
       </c>
       <c r="H67" t="str">
-        <v>2027-08-11</v>
+        <v>2027-08-10</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2759,16 +2759,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E68" t="str">
-        <v>2027-05-22</v>
+        <v>2027-05-21</v>
       </c>
       <c r="F68" t="str">
-        <v>2027-07-15</v>
+        <v>2027-07-14</v>
       </c>
       <c r="G68" t="str">
-        <v>2027-07-22</v>
+        <v>2027-07-21</v>
       </c>
       <c r="H68" t="str">
-        <v>2027-09-15</v>
+        <v>2027-09-14</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -2794,16 +2794,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E69" t="str">
-        <v>2027-06-26</v>
+        <v>2027-06-25</v>
       </c>
       <c r="F69" t="str">
-        <v>2027-08-19</v>
+        <v>2027-08-18</v>
       </c>
       <c r="G69" t="str">
-        <v>2027-08-26</v>
+        <v>2027-08-25</v>
       </c>
       <c r="H69" t="str">
-        <v>2027-10-20</v>
+        <v>2027-10-19</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -2829,16 +2829,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E70" t="str">
-        <v>2027-07-31</v>
+        <v>2027-07-30</v>
       </c>
       <c r="F70" t="str">
-        <v>2027-09-23</v>
+        <v>2027-09-22</v>
       </c>
       <c r="G70" t="str">
-        <v>2027-09-30</v>
+        <v>2027-09-29</v>
       </c>
       <c r="H70" t="str">
-        <v>2027-11-24</v>
+        <v>2027-11-23</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -2864,16 +2864,16 @@
         <v>R.R.H.H.</v>
       </c>
       <c r="E71" t="str">
-        <v>2027-09-04</v>
+        <v>2027-09-03</v>
       </c>
       <c r="F71" t="str">
-        <v>2027-10-28</v>
+        <v>2027-10-27</v>
       </c>
       <c r="G71" t="str">
-        <v>2027-11-04</v>
+        <v>2027-11-03</v>
       </c>
       <c r="H71" t="str">
-        <v>2027-12-29</v>
+        <v>2027-12-28</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -2899,16 +2899,16 @@
         <v>Dirección</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-11-28</v>
+        <v>2026-11-27</v>
       </c>
       <c r="F72" t="str">
-        <v>2026-11-28</v>
+        <v>2026-11-27</v>
       </c>
       <c r="G72" t="str">
-        <v>2027-01-30</v>
+        <v>2027-01-29</v>
       </c>
       <c r="H72" t="str">
-        <v>2027-01-30</v>
+        <v>2027-01-29</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -2934,16 +2934,16 @@
         <v>Dirección</v>
       </c>
       <c r="E73" t="str">
-        <v>2027-02-13</v>
+        <v>2027-02-12</v>
       </c>
       <c r="F73" t="str">
-        <v>2027-02-13</v>
+        <v>2027-02-12</v>
       </c>
       <c r="G73" t="str">
-        <v>2027-04-13</v>
+        <v>2027-04-12</v>
       </c>
       <c r="H73" t="str">
-        <v>2027-04-13</v>
+        <v>2027-04-12</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -2969,16 +2969,16 @@
         <v>Dirección</v>
       </c>
       <c r="E74" t="str">
-        <v>2027-03-13</v>
+        <v>2027-03-12</v>
       </c>
       <c r="F74" t="str">
-        <v>2027-03-13</v>
+        <v>2027-03-12</v>
       </c>
       <c r="G74" t="str">
-        <v>2027-05-13</v>
+        <v>2027-05-12</v>
       </c>
       <c r="H74" t="str">
-        <v>2027-05-13</v>
+        <v>2027-05-12</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3004,16 +3004,16 @@
         <v>Dirección</v>
       </c>
       <c r="E75" t="str">
-        <v>2027-04-17</v>
+        <v>2027-04-16</v>
       </c>
       <c r="F75" t="str">
-        <v>2027-04-17</v>
+        <v>2027-04-16</v>
       </c>
       <c r="G75" t="str">
-        <v>2027-06-17</v>
+        <v>2027-06-16</v>
       </c>
       <c r="H75" t="str">
-        <v>2027-06-17</v>
+        <v>2027-06-16</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3039,16 +3039,16 @@
         <v>Dirección</v>
       </c>
       <c r="E76" t="str">
-        <v>2027-05-22</v>
+        <v>2027-05-21</v>
       </c>
       <c r="F76" t="str">
-        <v>2027-05-22</v>
+        <v>2027-05-21</v>
       </c>
       <c r="G76" t="str">
-        <v>2027-07-22</v>
+        <v>2027-07-21</v>
       </c>
       <c r="H76" t="str">
-        <v>2027-07-22</v>
+        <v>2027-07-21</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3074,16 +3074,16 @@
         <v>Dirección</v>
       </c>
       <c r="E77" t="str">
-        <v>2027-06-26</v>
+        <v>2027-06-25</v>
       </c>
       <c r="F77" t="str">
-        <v>2027-06-26</v>
+        <v>2027-06-25</v>
       </c>
       <c r="G77" t="str">
-        <v>2027-08-26</v>
+        <v>2027-08-25</v>
       </c>
       <c r="H77" t="str">
-        <v>2027-08-26</v>
+        <v>2027-08-25</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3109,16 +3109,16 @@
         <v>Dirección</v>
       </c>
       <c r="E78" t="str">
-        <v>2027-07-31</v>
+        <v>2027-07-30</v>
       </c>
       <c r="F78" t="str">
-        <v>2027-07-31</v>
+        <v>2027-07-30</v>
       </c>
       <c r="G78" t="str">
-        <v>2027-09-30</v>
+        <v>2027-09-29</v>
       </c>
       <c r="H78" t="str">
-        <v>2027-09-30</v>
+        <v>2027-09-29</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3144,16 +3144,16 @@
         <v>Dirección</v>
       </c>
       <c r="E79" t="str">
-        <v>2027-09-03</v>
+        <v>2027-09-02</v>
       </c>
       <c r="F79" t="str">
-        <v>2027-09-03</v>
+        <v>2027-09-02</v>
       </c>
       <c r="G79" t="str">
-        <v>2027-11-03</v>
+        <v>2027-11-02</v>
       </c>
       <c r="H79" t="str">
-        <v>2027-11-03</v>
+        <v>2027-11-02</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3179,16 +3179,16 @@
         <v>Dirección</v>
       </c>
       <c r="E80" t="str">
-        <v>2027-10-09</v>
+        <v>2027-10-08</v>
       </c>
       <c r="F80" t="str">
-        <v>2027-10-09</v>
+        <v>2027-10-08</v>
       </c>
       <c r="G80" t="str">
-        <v>2027-12-09</v>
+        <v>2027-12-08</v>
       </c>
       <c r="H80" t="str">
-        <v>2027-12-09</v>
+        <v>2027-12-08</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3214,16 +3214,16 @@
         <v>Dirección</v>
       </c>
       <c r="E81" t="str">
-        <v>2027-11-13</v>
+        <v>2027-11-12</v>
       </c>
       <c r="F81" t="str">
-        <v>2027-11-13</v>
+        <v>2027-11-12</v>
       </c>
       <c r="G81" t="str">
-        <v>2028-01-13</v>
+        <v>2028-01-12</v>
       </c>
       <c r="H81" t="str">
-        <v>2028-01-13</v>
+        <v>2028-01-12</v>
       </c>
       <c r="I81">
         <v>0</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -496,10 +496,10 @@
         <v>2026-05-15</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="J3" t="str">
-        <v>Completado</v>
+        <v>En progreso</v>
       </c>
       <c r="K3" t="str">
         <v/>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -461,10 +461,10 @@
         <v>2026-05-15</v>
       </c>
       <c r="I2">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="J2" t="str">
-        <v>En progreso</v>
+        <v>Completado</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -496,10 +496,10 @@
         <v>2026-05-15</v>
       </c>
       <c r="I3">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="J3" t="str">
-        <v>En progreso</v>
+        <v>Completado</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -881,7 +881,7 @@
         <v>2026-09-25</v>
       </c>
       <c r="I14">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="str">
         <v>En progreso</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -461,10 +461,10 @@
         <v>2026-05-15</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="J2" t="str">
-        <v>Completado</v>
+        <v>En progreso</v>
       </c>
       <c r="K2" t="str">
         <v/>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -496,10 +496,10 @@
         <v>2026-05-15</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="J3" t="str">
-        <v>Completado</v>
+        <v>En progreso</v>
       </c>
       <c r="K3" t="str">
         <v/>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -881,7 +881,7 @@
         <v>2026-09-25</v>
       </c>
       <c r="I14">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J14" t="str">
         <v>En progreso</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -461,10 +461,10 @@
         <v>2026-05-15</v>
       </c>
       <c r="I2">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="J2" t="str">
-        <v>En progreso</v>
+        <v>Completado</v>
       </c>
       <c r="K2" t="str">
         <v/>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -496,10 +496,10 @@
         <v>2026-05-15</v>
       </c>
       <c r="I3">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="J3" t="str">
-        <v>En progreso</v>
+        <v>Completado</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -531,7 +531,7 @@
         <v>2026-07-06</v>
       </c>
       <c r="I4">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="str">
         <v>En progreso</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -881,7 +881,7 @@
         <v>2026-09-25</v>
       </c>
       <c r="I14">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="str">
         <v>En progreso</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -881,7 +881,7 @@
         <v>2026-09-25</v>
       </c>
       <c r="I14">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J14" t="str">
         <v>En progreso</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -881,7 +881,7 @@
         <v>2026-09-25</v>
       </c>
       <c r="I14">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="str">
         <v>En progreso</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -531,10 +531,10 @@
         <v>2026-07-06</v>
       </c>
       <c r="I4">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J4" t="str">
-        <v>En progreso</v>
+        <v>Completado</v>
       </c>
       <c r="K4" t="str">
         <v/>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -531,10 +531,10 @@
         <v>2026-07-06</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="str">
-        <v>Completado</v>
+        <v>Pendiente</v>
       </c>
       <c r="K4" t="str">
         <v/>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -531,10 +531,10 @@
         <v>2026-07-06</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J4" t="str">
-        <v>Pendiente</v>
+        <v>En progreso</v>
       </c>
       <c r="K4" t="str">
         <v/>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -461,10 +461,10 @@
         <v>2026-05-15</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J2" t="str">
-        <v>Completado</v>
+        <v>En progreso</v>
       </c>
       <c r="K2" t="str">
         <v/>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -461,10 +461,10 @@
         <v>2026-05-15</v>
       </c>
       <c r="I2">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="J2" t="str">
-        <v>En progreso</v>
+        <v>Completado</v>
       </c>
       <c r="K2" t="str">
         <v/>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -881,7 +881,7 @@
         <v>2026-09-25</v>
       </c>
       <c r="I14">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="str">
         <v>En progreso</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -881,7 +881,7 @@
         <v>2026-09-25</v>
       </c>
       <c r="I14">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="str">
         <v>En progreso</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -881,7 +881,7 @@
         <v>2026-09-25</v>
       </c>
       <c r="I14">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="str">
         <v>En progreso</v>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -601,7 +601,7 @@
         <v>2026-07-10</v>
       </c>
       <c r="I6">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="str">
         <v>En progreso</v>
@@ -636,7 +636,7 @@
         <v>2026-07-14</v>
       </c>
       <c r="I7">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="str">
         <v>En progreso</v>
@@ -671,7 +671,7 @@
         <v>2026-07-17</v>
       </c>
       <c r="I8">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="str">
         <v>En progreso</v>
@@ -706,10 +706,10 @@
         <v>2026-07-22</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="str">
-        <v>Pendiente</v>
+        <v>En progreso</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -741,10 +741,10 @@
         <v>2026-07-27</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J10" t="str">
-        <v>Pendiente</v>
+        <v>En progreso</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -776,10 +776,10 @@
         <v>2026-07-31</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="str">
-        <v>Pendiente</v>
+        <v>En progreso</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -881,10 +881,10 @@
         <v>2026-09-25</v>
       </c>
       <c r="I14">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J14" t="str">
-        <v>En progreso</v>
+        <v>Completado</v>
       </c>
       <c r="K14" t="str">
         <v/>

--- a/Cronograma_Fase2_ABA.xlsx
+++ b/Cronograma_Fase2_ABA.xlsx
@@ -531,10 +531,10 @@
         <v>2026-07-06</v>
       </c>
       <c r="I4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J4" t="str">
-        <v>En progreso</v>
+        <v>Completado</v>
       </c>
       <c r="K4" t="str">
         <v/>
